--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
   <si>
     <t>setting_name</t>
   </si>
@@ -456,9 +456,6 @@
   </si>
   <si>
     <t>Informador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itner {{data.interval}}   lasdtfusus {{calculates.displayLASTFUSUC}}    datasue  {{calculates.displaySeg}}</t>
   </si>
   <si>
     <t>sim/nao/naosabe</t>
@@ -7242,17 +7239,15 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="9" t="s">
-        <v>70</v>
-      </c>
+      <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="9" t="s">
-        <v>142</v>
-      </c>
+      <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -7264,7 +7259,7 @@
     <row r="6" ht="14.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -7282,15 +7277,23 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -7301,23 +7304,17 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>146</v>
       </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -7328,22 +7325,32 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>149</v>
+      </c>
       <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>150</v>
+      </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
@@ -7352,45 +7359,35 @@
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="7"/>
+        <v>153</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>154</v>
+      </c>
       <c r="F10" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>150</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="7" t="s">
-        <v>151</v>
-      </c>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>153</v>
-      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="B11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>156</v>
       </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -7403,18 +7400,20 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="I12" s="2" t="s">
+        <v>157</v>
+      </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -7424,20 +7423,16 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -7448,9 +7443,11 @@
     <row r="14" ht="14.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>158</v>
+      </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -7466,17 +7463,21 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -7490,54 +7491,48 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>166</v>
+      </c>
       <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c r="L16" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="7" t="s">
-        <v>160</v>
-      </c>
+      <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>166</v>
-      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="7" t="s">
-        <v>167</v>
-      </c>
+      <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>169</v>
-      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
@@ -7563,7 +7558,7 @@
     <row r="19" ht="14.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -7580,23 +7575,7 @@
       <c r="O19" s="7"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" ht="14.25">
       <c r="H21" s="2"/>
@@ -7605,95 +7584,96 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="H23" s="2"/>
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
         <v>170</v>
+      </c>
+      <c r="H24" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="D25" t="s">
-        <v>70</v>
+        <v>172</v>
+      </c>
+      <c r="E25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" t="s">
+        <v>173</v>
       </c>
       <c r="G25" t="s">
-        <v>171</v>
-      </c>
-      <c r="H25" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="D26" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" t="s">
-        <v>175</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="G26"/>
     </row>
     <row r="27" ht="14.25">
       <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>176</v>
+      </c>
       <c r="D27"/>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
-      <c r="H27"/>
+      <c r="H27" s="2"/>
       <c r="I27"/>
       <c r="J27"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>177</v>
-      </c>
       <c r="H28" s="2"/>
       <c r="O28"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="E29"/>
-      <c r="H29" s="2"/>
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" ht="14.25">
       <c r="B31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31"/>
       <c r="E31"/>
@@ -7703,729 +7683,745 @@
     </row>
     <row r="32" ht="14.25">
       <c r="B32" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H32" s="2"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="H33" s="2"/>
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" t="s">
+        <v>170</v>
+      </c>
+      <c r="H33" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="34" ht="14.25">
       <c r="D34" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E34" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
       </c>
       <c r="G34" t="s">
-        <v>171</v>
-      </c>
-      <c r="H34" t="s">
-        <v>172</v>
+        <v>183</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="D35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" t="s">
-        <v>184</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
         <v>185</v>
       </c>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="2"/>
+      <c r="G36" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="D37" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F37" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" t="s">
-        <v>180</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>182</v>
+      <c r="B37" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="38" ht="14.25">
       <c r="B38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="B39" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="B40" t="s">
+      <c r="D40" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" t="s">
         <v>170</v>
+      </c>
+      <c r="H40" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="D41" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E41" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" t="s">
+        <v>187</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
-      </c>
-      <c r="H41" t="s">
-        <v>172</v>
+        <v>188</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="D42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" t="s">
-        <v>188</v>
-      </c>
-      <c r="G42" t="s">
-        <v>189</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="B43" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>191</v>
       </c>
+      <c r="E43" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" t="s">
+        <v>192</v>
+      </c>
+      <c r="G43" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="D44" t="s">
-        <v>192</v>
-      </c>
-      <c r="E44" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44" t="s">
-        <v>193</v>
-      </c>
-      <c r="G44" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>182</v>
+      <c r="B44" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="B45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="14.25">
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="D47" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" t="s">
+        <v>171</v>
+      </c>
+      <c r="O47"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="D50" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="B51" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25">
-      <c r="B46" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" ht="14.25">
-      <c r="B47" t="s">
-        <v>37</v>
-      </c>
-      <c r="O47"/>
-    </row>
-    <row r="48" ht="14.25">
-      <c r="D48" t="s">
-        <v>70</v>
-      </c>
-      <c r="G48" t="s">
-        <v>171</v>
-      </c>
-      <c r="H48" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
-    </row>
-    <row r="50" ht="14.25">
-      <c r="B50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25">
-      <c r="D51" t="s">
-        <v>192</v>
-      </c>
-      <c r="E51" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="52" ht="14.25">
       <c r="B52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" ht="14.25">
       <c r="B53" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="B54" t="s">
+      <c r="D54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G54" t="s">
         <v>170</v>
+      </c>
+      <c r="H54" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="55" ht="14.25">
       <c r="D55" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E55" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" t="s">
+        <v>198</v>
       </c>
       <c r="G55" t="s">
-        <v>171</v>
-      </c>
-      <c r="H55" t="s">
-        <v>172</v>
+        <v>199</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="D56" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" t="s">
-        <v>143</v>
-      </c>
-      <c r="F56" t="s">
-        <v>199</v>
-      </c>
-      <c r="G56" t="s">
-        <v>200</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s">
         <v>201</v>
       </c>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="B57" t="s">
-        <v>35</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
+        <v>191</v>
+      </c>
+      <c r="E57" t="s">
+        <v>177</v>
+      </c>
+      <c r="F57" t="s">
         <v>202</v>
       </c>
-      <c r="H57" s="2"/>
+      <c r="G57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="D58" t="s">
-        <v>192</v>
-      </c>
-      <c r="E58" t="s">
-        <v>178</v>
-      </c>
-      <c r="F58" t="s">
-        <v>203</v>
-      </c>
-      <c r="G58" t="s">
-        <v>180</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>182</v>
+      <c r="B58" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="B59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="B60" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" ht="14.25">
-      <c r="B61" t="s">
-        <v>37</v>
+      <c r="D61" t="s">
+        <v>70</v>
+      </c>
+      <c r="G61" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="62" ht="14.25">
       <c r="D62" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E62" t="s">
+        <v>142</v>
+      </c>
+      <c r="F62" t="s">
+        <v>203</v>
       </c>
       <c r="G62" t="s">
-        <v>171</v>
-      </c>
-      <c r="H62" t="s">
-        <v>172</v>
+        <v>204</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="D63" t="s">
-        <v>62</v>
-      </c>
-      <c r="E63" t="s">
-        <v>143</v>
-      </c>
-      <c r="F63" t="s">
-        <v>204</v>
-      </c>
-      <c r="G63" t="s">
-        <v>205</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s">
         <v>206</v>
       </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="B64" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" t="s">
         <v>207</v>
       </c>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
+      <c r="G64" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="65" ht="14.25">
-      <c r="D65" t="s">
-        <v>154</v>
-      </c>
-      <c r="E65" t="s">
-        <v>178</v>
-      </c>
-      <c r="F65" t="s">
-        <v>208</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>182</v>
+      <c r="B65" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="66" ht="14.25">
       <c r="B66" t="s">
-        <v>52</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
     </row>
     <row r="67" ht="14.25">
       <c r="B67" t="s">
-        <v>51</v>
-      </c>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
+        <v>37</v>
+      </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="B68" t="s">
-        <v>37</v>
+      <c r="D68" t="s">
+        <v>70</v>
+      </c>
+      <c r="G68" t="s">
+        <v>170</v>
+      </c>
+      <c r="H68" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="69" ht="14.25">
       <c r="D69" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E69" t="s">
+        <v>142</v>
+      </c>
+      <c r="F69" t="s">
+        <v>208</v>
       </c>
       <c r="G69" t="s">
-        <v>171</v>
-      </c>
-      <c r="H69" t="s">
-        <v>172</v>
+        <v>209</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="70" ht="14.25">
-      <c r="D70" t="s">
-        <v>62</v>
-      </c>
-      <c r="E70" t="s">
-        <v>143</v>
-      </c>
-      <c r="F70" t="s">
-        <v>209</v>
-      </c>
-      <c r="G70" t="s">
-        <v>210</v>
-      </c>
-      <c r="H70" s="2" t="s">
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
         <v>211</v>
       </c>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="B71" t="s">
-        <v>35</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" t="s">
         <v>212</v>
       </c>
-      <c r="H71" s="2"/>
+      <c r="G71" t="s">
+        <v>179</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="72" ht="14.25">
-      <c r="D72" t="s">
-        <v>154</v>
-      </c>
-      <c r="E72" t="s">
-        <v>178</v>
-      </c>
-      <c r="F72" t="s">
-        <v>213</v>
-      </c>
-      <c r="G72" t="s">
-        <v>180</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>182</v>
+      <c r="B72" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="73" ht="14.25">
       <c r="B73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" ht="14.25">
       <c r="B74" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" ht="14.25">
-      <c r="B75" t="s">
-        <v>37</v>
+      <c r="D75" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" t="s">
+        <v>170</v>
+      </c>
+      <c r="H75" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="76" ht="14.25">
       <c r="D76" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E76" t="s">
+        <v>142</v>
+      </c>
+      <c r="F76" t="s">
+        <v>213</v>
       </c>
       <c r="G76" t="s">
-        <v>171</v>
-      </c>
-      <c r="H76" t="s">
-        <v>172</v>
+        <v>214</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="77" ht="14.25">
-      <c r="D77" t="s">
-        <v>62</v>
-      </c>
-      <c r="E77" t="s">
-        <v>143</v>
-      </c>
-      <c r="F77" t="s">
-        <v>214</v>
-      </c>
-      <c r="G77" t="s">
-        <v>215</v>
-      </c>
-      <c r="H77" s="2" t="s">
+      <c r="B77" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" t="s">
         <v>216</v>
       </c>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="B78" t="s">
-        <v>35</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" t="s">
         <v>217</v>
       </c>
-      <c r="H78" s="2"/>
+      <c r="G78" t="s">
+        <v>179</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="79" ht="14.25">
-      <c r="D79" t="s">
-        <v>154</v>
-      </c>
-      <c r="E79" t="s">
-        <v>178</v>
-      </c>
-      <c r="F79" t="s">
-        <v>218</v>
-      </c>
-      <c r="G79" t="s">
-        <v>180</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>182</v>
+      <c r="B79" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="80" ht="14.25">
       <c r="B80" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" ht="14.25">
       <c r="B81" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" ht="14.25">
-      <c r="B82" t="s">
-        <v>37</v>
+      <c r="D82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G82" t="s">
+        <v>170</v>
+      </c>
+      <c r="H82" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="83" ht="14.25">
       <c r="D83" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E83" t="s">
+        <v>142</v>
+      </c>
+      <c r="F83" t="s">
+        <v>218</v>
       </c>
       <c r="G83" t="s">
-        <v>171</v>
-      </c>
-      <c r="H83" t="s">
-        <v>172</v>
+        <v>219</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="84" ht="14.25">
-      <c r="D84" t="s">
-        <v>62</v>
-      </c>
-      <c r="E84" t="s">
-        <v>143</v>
-      </c>
-      <c r="F84" t="s">
-        <v>219</v>
-      </c>
-      <c r="G84" t="s">
-        <v>220</v>
-      </c>
-      <c r="H84" s="2" t="s">
+      <c r="B84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" t="s">
         <v>221</v>
       </c>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="B85" t="s">
-        <v>35</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>222</v>
       </c>
-      <c r="H85" s="2"/>
+      <c r="F85" t="s">
+        <v>223</v>
+      </c>
+      <c r="G85" t="s">
+        <v>224</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="86" ht="14.25">
       <c r="D86" t="s">
-        <v>223</v>
+        <v>153</v>
+      </c>
+      <c r="E86" t="s">
+        <v>177</v>
       </c>
       <c r="F86" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G86" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>226</v>
+        <v>180</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="87" ht="14.25">
-      <c r="D87" t="s">
-        <v>154</v>
-      </c>
-      <c r="E87" t="s">
-        <v>178</v>
-      </c>
-      <c r="F87" t="s">
-        <v>227</v>
-      </c>
-      <c r="G87" t="s">
-        <v>180</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>182</v>
+      <c r="B87" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="88" ht="14.25">
       <c r="B88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" ht="14.25">
       <c r="B89" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" ht="14.25">
-      <c r="B90" t="s">
-        <v>37</v>
+      <c r="D90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" t="s">
+        <v>170</v>
+      </c>
+      <c r="H90" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="91" ht="14.25">
       <c r="D91" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="E91" t="s">
+        <v>142</v>
+      </c>
+      <c r="F91" t="s">
+        <v>227</v>
       </c>
       <c r="G91" t="s">
-        <v>171</v>
-      </c>
-      <c r="H91" t="s">
-        <v>172</v>
+        <v>228</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="92" ht="14.25">
-      <c r="D92" t="s">
-        <v>62</v>
-      </c>
-      <c r="E92" t="s">
-        <v>143</v>
-      </c>
-      <c r="F92" t="s">
-        <v>228</v>
-      </c>
-      <c r="G92" t="s">
-        <v>229</v>
-      </c>
-      <c r="H92" s="2" t="s">
+      <c r="B92" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" t="s">
         <v>230</v>
       </c>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="B93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
+        <v>153</v>
+      </c>
+      <c r="E93" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" t="s">
         <v>231</v>
       </c>
-      <c r="H93" s="2"/>
+      <c r="G93" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="94" ht="14.25">
       <c r="D94" t="s">
-        <v>154</v>
-      </c>
-      <c r="E94" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="F94" t="s">
         <v>232</v>
       </c>
       <c r="G94" t="s">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" ht="14.25">
       <c r="D95" t="s">
-        <v>223</v>
+        <v>62</v>
+      </c>
+      <c r="E95" t="s">
+        <v>235</v>
       </c>
       <c r="F95" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G95" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" ht="14.25">
-      <c r="D96" t="s">
-        <v>62</v>
-      </c>
-      <c r="E96" t="s">
-        <v>236</v>
-      </c>
-      <c r="F96" t="s">
-        <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>238</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>239</v>
+      <c r="B96" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="97" ht="14.25">
       <c r="B97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O97"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="B98" t="s">
-        <v>51</v>
-      </c>
-      <c r="O98"/>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="7"/>
     </row>
     <row r="99" ht="14.25">
       <c r="A99" s="2"/>
-      <c r="B99" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="B99" s="2"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
+      <c r="D99" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
+      <c r="G99" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="I99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
@@ -8439,15 +8435,19 @@
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="G100" s="2" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="I100" s="2"/>
       <c r="K100" s="2"/>
@@ -8459,23 +8459,17 @@
     </row>
     <row r="101" ht="14.25">
       <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H101" s="2" t="s">
+      <c r="B101" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>242</v>
       </c>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
@@ -8486,19 +8480,27 @@
     </row>
     <row r="102" ht="14.25">
       <c r="A102" s="2"/>
-      <c r="B102" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
+      <c r="G102" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="I102" s="2"/>
-      <c r="K102" s="2"/>
+      <c r="K102" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="L102" s="2"/>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -8507,27 +8509,16 @@
     </row>
     <row r="103" ht="14.25">
       <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I103" s="2"/>
-      <c r="K103" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="7"/>
       <c r="L103" s="2"/>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
@@ -8538,11 +8529,21 @@
       <c r="A104" s="2"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
-      <c r="H104" s="14"/>
+      <c r="D104" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="I104" s="14"/>
       <c r="J104" s="14"/>
       <c r="K104" s="7"/>
@@ -8554,23 +8555,17 @@
     </row>
     <row r="105" ht="14.25">
       <c r="A105" s="2"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G105" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H105" s="14" t="s">
+      <c r="B105" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" s="14" t="s">
         <v>248</v>
       </c>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
       <c r="K105" s="7"/>
@@ -8582,17 +8577,21 @@
     </row>
     <row r="106" ht="14.25">
       <c r="A106" s="2"/>
-      <c r="B106" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C106" s="14" t="s">
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
+      <c r="G106" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>251</v>
+      </c>
       <c r="I106" s="14"/>
       <c r="J106" s="14"/>
       <c r="K106" s="7"/>
@@ -8604,21 +8603,15 @@
     </row>
     <row r="107" ht="14.25">
       <c r="A107" s="2"/>
-      <c r="B107" s="14"/>
+      <c r="B107" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="C107" s="14"/>
-      <c r="D107" s="14" t="s">
-        <v>223</v>
-      </c>
+      <c r="D107" s="14"/>
       <c r="E107" s="14"/>
-      <c r="F107" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="G107" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="H107" s="14" t="s">
-        <v>252</v>
-      </c>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
       <c r="K107" s="7"/>
@@ -8630,9 +8623,7 @@
     </row>
     <row r="108" ht="14.25">
       <c r="A108" s="2"/>
-      <c r="B108" s="14" t="s">
-        <v>52</v>
-      </c>
+      <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -8650,15 +8641,17 @@
     </row>
     <row r="109" ht="14.25">
       <c r="A109" s="2"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
-      <c r="I109" s="14"/>
-      <c r="J109" s="14"/>
+      <c r="B109" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
       <c r="K109" s="7"/>
       <c r="L109" s="2"/>
       <c r="M109" s="7"/>
@@ -8669,7 +8662,7 @@
     <row r="110" ht="14.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -8686,29 +8679,9 @@
       <c r="O110" s="7"/>
       <c r="P110" s="7"/>
     </row>
-    <row r="111" ht="14.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="2"/>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="7"/>
-    </row>
+    <row r="111" ht="14.25"/>
     <row r="112" ht="14.25"/>
     <row r="113" ht="14.25"/>
-    <row r="114" ht="14.25"/>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
@@ -8733,10 +8706,10 @@
   <sheetData>
     <row r="1" s="15" customFormat="1" ht="14.25">
       <c r="A1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8745,38 +8718,38 @@
         <v>3</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="G2" s="11"/>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
@@ -8784,17 +8757,17 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="12" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
         <v>260</v>
-      </c>
-      <c r="D4" t="s">
-        <v>261</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
@@ -8802,33 +8775,33 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="G5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="14.25">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="G6" s="11"/>
     </row>
@@ -8841,13 +8814,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="G7" s="11"/>
     </row>
@@ -8860,10 +8833,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -8880,10 +8853,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -8900,10 +8873,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G10" s="11"/>
     </row>
@@ -8916,10 +8889,10 @@
         <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G11" s="11"/>
     </row>
@@ -8932,372 +8905,372 @@
         <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G12" s="11"/>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B13" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E13" t="s">
         <v>269</v>
-      </c>
-      <c r="D13" t="s">
-        <v>269</v>
-      </c>
-      <c r="E13" t="s">
-        <v>270</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B14" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" t="s">
         <v>271</v>
-      </c>
-      <c r="D14" t="s">
-        <v>271</v>
-      </c>
-      <c r="E14" t="s">
-        <v>272</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B15" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C15" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" t="s">
         <v>273</v>
-      </c>
-      <c r="D15" t="s">
-        <v>273</v>
-      </c>
-      <c r="E15" t="s">
-        <v>274</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B16" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E16" t="s">
         <v>275</v>
-      </c>
-      <c r="D16" t="s">
-        <v>275</v>
-      </c>
-      <c r="E16" t="s">
-        <v>276</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B17" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D17" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" t="s">
         <v>277</v>
-      </c>
-      <c r="D17" t="s">
-        <v>277</v>
-      </c>
-      <c r="E17" t="s">
-        <v>278</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B18" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C18" t="s">
+        <v>278</v>
+      </c>
+      <c r="D18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18" t="s">
         <v>279</v>
-      </c>
-      <c r="D18" t="s">
-        <v>279</v>
-      </c>
-      <c r="E18" t="s">
-        <v>280</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B19" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B20" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B21" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B23" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" t="s">
         <v>287</v>
-      </c>
-      <c r="D25" t="s">
-        <v>287</v>
-      </c>
-      <c r="E25" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B26" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C26" t="s">
+        <v>288</v>
+      </c>
+      <c r="D26" t="s">
+        <v>288</v>
+      </c>
+      <c r="E26" t="s">
         <v>289</v>
-      </c>
-      <c r="D26" t="s">
-        <v>289</v>
-      </c>
-      <c r="E26" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B27" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" t="s">
         <v>291</v>
-      </c>
-      <c r="D27" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B28" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C28" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" t="s">
         <v>293</v>
-      </c>
-      <c r="D28" t="s">
-        <v>293</v>
-      </c>
-      <c r="E28" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B29" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C29" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29" t="s">
+        <v>294</v>
+      </c>
+      <c r="E29" t="s">
         <v>295</v>
-      </c>
-      <c r="D29" t="s">
-        <v>295</v>
-      </c>
-      <c r="E29" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B30" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C30" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E30" t="s">
         <v>297</v>
-      </c>
-      <c r="D30" t="s">
-        <v>297</v>
-      </c>
-      <c r="E30" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B31" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" t="s">
         <v>299</v>
-      </c>
-      <c r="D31" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="32" ht="14.25">
@@ -9309,10 +9282,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>301</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="33" ht="14.25">
@@ -9324,10 +9297,10 @@
         <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="34" ht="14.25">
@@ -9339,10 +9312,10 @@
         <v>3</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="35" ht="14.25">
@@ -9354,10 +9327,10 @@
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="36" ht="14.25">
@@ -9369,10 +9342,10 @@
         <v>5</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="37" ht="14.25">
@@ -9384,10 +9357,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="38" ht="14.25">
@@ -9399,10 +9372,10 @@
         <v>2</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="39" ht="14.25">
@@ -9414,25 +9387,25 @@
         <v>3</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>"99"</f>
         <v>99</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" ht="14.25">
@@ -9672,7 +9645,7 @@
   <sheetData>
     <row r="1" ht="14.5">
       <c r="A1" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>29</v>
@@ -9680,82 +9653,82 @@
     </row>
     <row r="2" ht="14.5">
       <c r="A2" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="3" ht="14.5">
       <c r="A3" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>321</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="4" ht="14.5">
       <c r="A4" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>323</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="5" ht="14.5">
       <c r="A5" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>325</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="6" ht="14.5">
       <c r="A6" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>327</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="7" ht="14.5">
       <c r="A7" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>329</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="8" ht="14.5">
       <c r="A8" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>331</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="9" ht="14.5">
       <c r="A9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>333</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="10" ht="14.5">
       <c r="A10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>335</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="11" ht="14.5">
       <c r="A11" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>337</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="12" ht="14.5">
@@ -9885,44 +9858,44 @@
   <sheetData>
     <row r="1" s="15" customFormat="1" ht="14.5">
       <c r="A1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="2" ht="122.34999999999999">
       <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
         <v>343</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>344</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="3" ht="68.650000000000006">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" t="s">
         <v>344</v>
       </c>
-      <c r="C3" t="s">
-        <v>345</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" ht="122.34999999999999">
@@ -9955,16 +9928,16 @@
   <sheetData>
     <row r="1" s="11" customFormat="1" ht="14.5">
       <c r="A1" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>349</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" ht="14.5">
@@ -9972,13 +9945,13 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2" t="s">
         <v>351</v>
-      </c>
-      <c r="C2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D2" t="s">
-        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -10011,10 +9984,10 @@
         <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="14.25">
@@ -10201,7 +10174,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="14.25">
       <c r="A16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>62</v>
@@ -10237,15 +10210,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C19" s="20" t="b">
         <f t="shared" ref="C19:C20" si="1">FALSE()</f>
@@ -10255,10 +10228,10 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" s="20" t="b">
         <f t="shared" si="1"/>
@@ -10268,10 +10241,10 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="20" t="b">
         <f>TRUE()</f>
@@ -10281,10 +10254,10 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="11" t="b">
         <f>FALSE()</f>
@@ -10294,25 +10267,25 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="11" t="b">
         <f t="shared" ref="C23:C25" si="2">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="11" t="b">
         <f t="shared" si="2"/>
@@ -10322,10 +10295,10 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C25" s="11" t="b">
         <f t="shared" si="2"/>
@@ -10341,7 +10314,7 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B27" s="20" t="s">
         <v>48</v>
@@ -10354,10 +10327,10 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C28" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10367,10 +10340,10 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10380,10 +10353,10 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C30" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10393,10 +10366,10 @@
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C31" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10406,10 +10379,10 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C32" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10419,10 +10392,10 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C33" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10432,7 +10405,7 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>62</v>
@@ -10445,10 +10418,10 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10458,10 +10431,10 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C36" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10471,10 +10444,10 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C37" s="20" t="b">
         <f t="shared" si="3"/>
@@ -10484,10 +10457,10 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C38" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10497,10 +10470,10 @@
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C39" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10510,10 +10483,10 @@
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C40" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10523,10 +10496,10 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="14.25">
       <c r="A41" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C41" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10536,10 +10509,10 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="14.25">
       <c r="A42" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C42" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10549,7 +10522,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="14.25">
       <c r="A43" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>62</v>
@@ -10562,10 +10535,10 @@
     </row>
     <row r="44" s="1" customFormat="1" ht="14.25">
       <c r="A44" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C44" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10575,7 +10548,7 @@
     </row>
     <row r="45" s="1" customFormat="1" ht="14.25">
       <c r="A45" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>62</v>
@@ -10588,10 +10561,10 @@
     </row>
     <row r="46" s="1" customFormat="1" ht="14.25">
       <c r="A46" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10601,7 +10574,7 @@
     </row>
     <row r="47" s="1" customFormat="1" ht="14.25">
       <c r="A47" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>62</v>
@@ -10613,10 +10586,10 @@
     </row>
     <row r="48" s="1" customFormat="1" ht="14.25">
       <c r="A48" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C48" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10625,7 +10598,7 @@
     </row>
     <row r="49" s="1" customFormat="1" ht="14.25">
       <c r="A49" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>62</v>
@@ -10637,10 +10610,10 @@
     </row>
     <row r="50" s="1" customFormat="1" ht="14.25">
       <c r="A50" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C50" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10649,7 +10622,7 @@
     </row>
     <row r="51" s="1" customFormat="1" ht="14.25">
       <c r="A51" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>62</v>
@@ -10661,10 +10634,10 @@
     </row>
     <row r="52" s="1" customFormat="1" ht="14.25">
       <c r="A52" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C52" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10673,7 +10646,7 @@
     </row>
     <row r="53" s="1" customFormat="1" ht="14.25">
       <c r="A53" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>62</v>
@@ -10685,10 +10658,10 @@
     </row>
     <row r="54" s="1" customFormat="1" ht="14.25">
       <c r="A54" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C54" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10697,7 +10670,7 @@
     </row>
     <row r="55" s="1" customFormat="1" ht="14.25">
       <c r="A55" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
@@ -10709,10 +10682,10 @@
     </row>
     <row r="56" s="1" customFormat="1" ht="14.25">
       <c r="A56" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10721,7 +10694,7 @@
     </row>
     <row r="57" s="1" customFormat="1" ht="14.25">
       <c r="A57" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>62</v>
@@ -10733,10 +10706,10 @@
     </row>
     <row r="58" s="1" customFormat="1" ht="14.25">
       <c r="A58" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C58" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10745,10 +10718,10 @@
     </row>
     <row r="59" s="1" customFormat="1" ht="14.25">
       <c r="A59" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C59" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10757,7 +10730,7 @@
     </row>
     <row r="60" s="1" customFormat="1" ht="14.25">
       <c r="A60" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>62</v>
@@ -10769,10 +10742,10 @@
     </row>
     <row r="61" s="1" customFormat="1" ht="14.25">
       <c r="A61" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C61" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10781,10 +10754,10 @@
     </row>
     <row r="62" s="1" customFormat="1" ht="14.25">
       <c r="A62" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C62" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10793,7 +10766,7 @@
     </row>
     <row r="63" s="1" customFormat="1" ht="14.25">
       <c r="A63" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>62</v>
@@ -10805,7 +10778,7 @@
     </row>
     <row r="64" s="1" customFormat="1" ht="14.25">
       <c r="A64" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>62</v>
@@ -10817,10 +10790,10 @@
     </row>
     <row r="65" s="1" customFormat="1" ht="14.25">
       <c r="A65" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C65" s="1" t="b">
         <f t="shared" si="3"/>
@@ -10829,10 +10802,10 @@
     </row>
     <row r="66" s="1" customFormat="1" ht="14.25">
       <c r="A66" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C66" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10841,10 +10814,10 @@
     </row>
     <row r="67" s="1" customFormat="1" ht="14.25">
       <c r="A67" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C67" s="11" t="b">
         <f t="shared" si="3"/>
@@ -10863,7 +10836,7 @@
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>48</v>
@@ -10874,7 +10847,7 @@
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>48</v>
@@ -10885,7 +10858,7 @@
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>48</v>

--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566D751C-5F4E-4B5A-9794-B0E008776769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08428C3-A3B6-42C4-BC9A-7A7840D0D4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -75,12 +75,6 @@
     <t>survey</t>
   </si>
   <si>
-    <t>MADtrial - Follow-up Visit</t>
-  </si>
-  <si>
-    <t>MADtrial - Seguimento Visita</t>
-  </si>
-  <si>
     <t>default</t>
   </si>
   <si>
@@ -1149,6 +1143,12 @@
   </si>
   <si>
     <t>Inclusão/Último seguimento por telefone: &lt;b&gt;{{calculates.displayLASTFUSUC}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>MADtrial - AE Follow-up call</t>
+  </si>
+  <si>
+    <t>MADtrial - Seguimento Chamada EA</t>
   </si>
 </sst>
 </file>
@@ -1543,40 +1543,40 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
         <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
         <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1609,122 +1609,122 @@
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
         <v>38</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>43</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
         <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
       </c>
       <c r="L7" t="b">
         <f>FALSE()</f>
@@ -1737,82 +1737,82 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
         <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
         <v>42</v>
       </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
         <v>48</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
       </c>
       <c r="L15" t="b">
         <f>FALSE()</f>
@@ -1825,82 +1825,82 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
         <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" t="s">
         <v>42</v>
       </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" t="s">
-        <v>44</v>
-      </c>
       <c r="H21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" t="s">
         <v>48</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" t="s">
-        <v>50</v>
       </c>
       <c r="L23" t="b">
         <f>FALSE()</f>
@@ -1913,79 +1913,79 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
         <v>62</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="J28" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="K28" t="s">
         <v>66</v>
-      </c>
-      <c r="J28" t="s">
-        <v>67</v>
-      </c>
-      <c r="K28" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" t="s">
         <v>70</v>
-      </c>
-      <c r="G30" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I31">
         <v>4</v>
@@ -1993,189 +1993,189 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G48" s="7"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I53">
         <v>7</v>
@@ -2183,57 +2183,57 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F55" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="J55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H57" t="s">
         <v>70</v>
-      </c>
-      <c r="G57" t="s">
-        <v>71</v>
-      </c>
-      <c r="H57" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I58">
         <v>4</v>
@@ -2241,193 +2241,193 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D69" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G72" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G73" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O77" s="5"/>
     </row>
     <row r="78" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G80" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H80" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F81" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I81">
         <v>7</v>
@@ -2435,57 +2435,57 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F83" t="s">
+        <v>104</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="J83" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K83" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D85" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" t="s">
+        <v>69</v>
+      </c>
+      <c r="H85" t="s">
         <v>70</v>
-      </c>
-      <c r="G85" t="s">
-        <v>71</v>
-      </c>
-      <c r="H85" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D86" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I86">
         <v>4</v>
@@ -2493,233 +2493,233 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G88" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H88" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C89" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D90" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G90" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H90" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D92" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G92" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H92" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G95" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D97" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G97" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D99" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G99" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D100" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G100" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D101" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G101" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F102" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I102" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D110" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E110" t="s">
+        <v>61</v>
+      </c>
+      <c r="F110" t="s">
+        <v>109</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F110" t="s">
-        <v>111</v>
-      </c>
-      <c r="G110" s="2" t="s">
+      <c r="H110" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J110" t="s">
         <v>65</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="K110" t="s">
         <v>66</v>
-      </c>
-      <c r="J110" t="s">
-        <v>67</v>
-      </c>
-      <c r="K110" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C111" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D112" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" t="s">
         <v>70</v>
-      </c>
-      <c r="G112" t="s">
-        <v>71</v>
-      </c>
-      <c r="H112" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="113" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F113" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I113">
         <v>4</v>
@@ -2727,190 +2727,190 @@
     </row>
     <row r="114" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D115" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G115" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H115" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C116" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D117" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G117" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H117" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="119" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D119" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G119" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C121" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="122" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D122" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G122" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H122" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="124" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D124" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G124" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H124" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D126" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G126" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H126" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="127" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D127" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G127" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H127" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D128" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G128" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H128" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O128" s="5"/>
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D129" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F129" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I129" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G130" s="7"/>
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C131" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G131" s="7"/>
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C133" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D134" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G134" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H134" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D135" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F135" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I135">
         <v>7</v>
@@ -2918,57 +2918,57 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="137" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D137" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E137" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F137" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J137" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K137" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C138" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D139" t="s">
+        <v>68</v>
+      </c>
+      <c r="G139" t="s">
+        <v>69</v>
+      </c>
+      <c r="H139" t="s">
         <v>70</v>
-      </c>
-      <c r="G139" t="s">
-        <v>71</v>
-      </c>
-      <c r="H139" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F140" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I140">
         <v>4</v>
@@ -2976,192 +2976,192 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D142" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G142" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H142" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C143" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D144" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G144" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H144" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D146" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G146" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H146" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C148" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D149" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G149" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D151" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G151" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H151" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D153" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G153" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H153" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D154" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G154" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H154" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D155" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H155" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D156" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F156" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C159" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="160" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D162" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G162" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H162" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D163" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F163" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I163">
         <v>7</v>
@@ -3169,57 +3169,57 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="165" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D165" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E165" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F165" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J165" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K165" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C166" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D167" t="s">
+        <v>68</v>
+      </c>
+      <c r="G167" t="s">
+        <v>69</v>
+      </c>
+      <c r="H167" t="s">
         <v>70</v>
-      </c>
-      <c r="G167" t="s">
-        <v>71</v>
-      </c>
-      <c r="H167" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D168" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F168" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I168">
         <v>4</v>
@@ -3227,233 +3227,233 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D170" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H170" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C171" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D172" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G172" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H172" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D174" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G174" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H174" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C176" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D177" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G177" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H177" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D179" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G179" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H179" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D181" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G181" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H181" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D182" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G182" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H182" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D183" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G183" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H183" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D184" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F184" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I184" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B190" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C190" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D192" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E192" t="s">
+        <v>61</v>
+      </c>
+      <c r="F192" t="s">
+        <v>119</v>
+      </c>
+      <c r="G192" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F192" t="s">
-        <v>121</v>
-      </c>
-      <c r="G192" s="2" t="s">
+      <c r="H192" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J192" t="s">
         <v>65</v>
       </c>
-      <c r="H192" s="2" t="s">
+      <c r="K192" t="s">
         <v>66</v>
-      </c>
-      <c r="J192" t="s">
-        <v>67</v>
-      </c>
-      <c r="K192" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C193" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D194" t="s">
+        <v>68</v>
+      </c>
+      <c r="G194" t="s">
+        <v>69</v>
+      </c>
+      <c r="H194" t="s">
         <v>70</v>
-      </c>
-      <c r="G194" t="s">
-        <v>71</v>
-      </c>
-      <c r="H194" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D195" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F195" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I195">
         <v>4</v>
@@ -3461,189 +3461,189 @@
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D197" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G197" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H197" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C198" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D199" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G199" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H199" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D201" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G201" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H201" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C203" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D204" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G204" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H204" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D206" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G206" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H206" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D208" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G208" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H208" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G209" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H209" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D210" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G210" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H210" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D211" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F211" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I211" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G212" s="7"/>
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C213" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G213" s="7"/>
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C215" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D216" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G216" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H216" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D217" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F217" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I217">
         <v>7</v>
@@ -3651,57 +3651,57 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="219" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D219" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E219" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F219" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J219" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K219" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C220" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D221" t="s">
+        <v>68</v>
+      </c>
+      <c r="G221" t="s">
+        <v>69</v>
+      </c>
+      <c r="H221" t="s">
         <v>70</v>
-      </c>
-      <c r="G221" t="s">
-        <v>71</v>
-      </c>
-      <c r="H221" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D222" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F222" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I222">
         <v>4</v>
@@ -3709,192 +3709,192 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D224" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G224" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H224" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B225" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C225" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D226" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G226" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H226" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D228" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G228" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H228" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C230" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D231" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G231" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H231" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D233" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G233" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H233" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D235" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G235" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H235" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D236" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G236" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H236" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D237" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G237" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H237" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="238" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D238" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F238" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I238" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="239" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="240" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C241" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C243" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D244" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G244" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H244" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D245" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F245" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I245">
         <v>7</v>
@@ -3902,57 +3902,57 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B246" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="247" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D247" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E247" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F247" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J247" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K247" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C248" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D249" t="s">
+        <v>68</v>
+      </c>
+      <c r="G249" t="s">
+        <v>69</v>
+      </c>
+      <c r="H249" t="s">
         <v>70</v>
-      </c>
-      <c r="G249" t="s">
-        <v>71</v>
-      </c>
-      <c r="H249" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D250" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F250" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I250">
         <v>4</v>
@@ -3960,185 +3960,185 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D252" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G252" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H252" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C253" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D254" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G254" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H254" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="255" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D256" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G256" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H256" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="257" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="258" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C258" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="259" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D259" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G259" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H259" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="260" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="261" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D261" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G261" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H261" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="262" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="263" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D263" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G263" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H263" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="264" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D264" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G264" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H264" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="265" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D265" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G265" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H265" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="266" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D266" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F266" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I266" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="267" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="268" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="269" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B269" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="270" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="271" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="272" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C272" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="273" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B274" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4170,271 +4170,271 @@
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="O1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" t="s">
         <v>138</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>139</v>
-      </c>
-      <c r="G4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" t="s">
         <v>142</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>143</v>
-      </c>
-      <c r="G7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" t="s">
         <v>147</v>
       </c>
-      <c r="G9" t="s">
+      <c r="J9" t="s">
         <v>148</v>
       </c>
-      <c r="H9" t="s">
+      <c r="L9" t="s">
         <v>149</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>150</v>
-      </c>
-      <c r="L9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M9" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" t="s">
         <v>153</v>
-      </c>
-      <c r="E10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F10" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
         <v>159</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>160</v>
-      </c>
-      <c r="G15" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" t="s">
         <v>163</v>
       </c>
-      <c r="G16" t="s">
+      <c r="J16" t="s">
         <v>164</v>
       </c>
-      <c r="H16" t="s">
+      <c r="L16" t="s">
         <v>165</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>166</v>
-      </c>
-      <c r="L16" t="s">
-        <v>167</v>
-      </c>
-      <c r="M16" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" t="s">
         <v>171</v>
       </c>
-      <c r="E25" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" t="s">
-        <v>173</v>
-      </c>
       <c r="H25" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
@@ -4442,40 +4442,40 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G34" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.35">
@@ -4483,40 +4483,40 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H40" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.35">
@@ -4524,40 +4524,40 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F48" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G48" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H48" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.35">
@@ -4565,40 +4565,40 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G54" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H54" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F55" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H55" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.35">
@@ -4606,40 +4606,40 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G61" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H61" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E62" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F62" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G62" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H62" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.35">
@@ -4647,40 +4647,40 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H68" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F69" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G69" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H69" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.35">
@@ -4688,40 +4688,40 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D75" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G75" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H75" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E76" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G76" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H76" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.35">
@@ -4729,62 +4729,62 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D82" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G82" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F83" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H83" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D85" t="s">
+        <v>202</v>
+      </c>
+      <c r="F85" t="s">
+        <v>203</v>
+      </c>
+      <c r="G85" t="s">
         <v>204</v>
       </c>
-      <c r="F85" t="s">
+      <c r="H85" t="s">
         <v>205</v>
-      </c>
-      <c r="G85" t="s">
-        <v>206</v>
-      </c>
-      <c r="H85" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.35">
@@ -4792,143 +4792,143 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D90" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G90" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H90" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D91" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F91" t="s">
+        <v>207</v>
+      </c>
+      <c r="G91" t="s">
+        <v>208</v>
+      </c>
+      <c r="H91" t="s">
         <v>209</v>
-      </c>
-      <c r="G91" t="s">
-        <v>210</v>
-      </c>
-      <c r="H91" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E93" t="s">
+        <v>172</v>
+      </c>
+      <c r="F93" t="s">
+        <v>211</v>
+      </c>
+      <c r="G93" t="s">
         <v>174</v>
       </c>
-      <c r="F93" t="s">
-        <v>213</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
+        <v>175</v>
+      </c>
+      <c r="K93" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="H93" t="s">
-        <v>177</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D94" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F94" t="s">
+        <v>212</v>
+      </c>
+      <c r="G94" t="s">
+        <v>213</v>
+      </c>
+      <c r="H94" t="s">
         <v>214</v>
-      </c>
-      <c r="G94" t="s">
-        <v>215</v>
-      </c>
-      <c r="H94" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D99" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G99" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H99" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D100" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F100" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G100" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H100" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.35">
       <c r="K102" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.35">
@@ -4946,29 +4946,29 @@
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E104" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G104" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="H104" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I104" s="9"/>
       <c r="J104" s="9"/>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B105" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -4982,24 +4982,24 @@
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H106" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="G106" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H106" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="I106" s="9"/>
       <c r="J106" s="9"/>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B107" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -5023,12 +5023,12 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5050,10 +5050,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5062,153 +5062,153 @@
         <v>3</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B2" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B3" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B4" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B5" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B6" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B9" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G10" s="8"/>
     </row>
@@ -5220,476 +5220,476 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B13" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B14" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B15" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B16" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B17" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B18" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B19" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B20" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B21" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B22" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B23" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B24" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B25" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B26" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B27" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E27" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E28" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B29" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E29" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B30" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B31" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D31" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B32" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B33" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B34" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B35" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D35" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B36" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B37" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B38" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B40" t="str">
         <f>"99"</f>
         <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.35">
@@ -5804,90 +5804,90 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -5956,44 +5956,44 @@
   <sheetData>
     <row r="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" t="s">
         <v>317</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="J3" s="2"/>
     </row>
@@ -6022,30 +6022,30 @@
   <sheetData>
     <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>322</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6067,24 +6067,24 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="8" t="b">
         <f t="shared" ref="C2:C17" si="0">FALSE()</f>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="5" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6146,10 +6146,10 @@
     </row>
     <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="8" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="9" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C9" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="10" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="11" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="12" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="13" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6237,10 +6237,10 @@
     </row>
     <row r="14" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="C14" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="15" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6263,10 +6263,10 @@
     </row>
     <row r="16" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6276,10 +6276,10 @@
     </row>
     <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="8" t="b">
         <f t="shared" si="0"/>
@@ -6289,25 +6289,25 @@
     </row>
     <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C19" s="8" t="b">
         <f t="shared" ref="C19:C20" si="1">FALSE()</f>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C20" s="8" t="b">
         <f t="shared" si="1"/>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C21" s="8" t="b">
         <f>TRUE()</f>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" s="8" t="b">
         <f>FALSE()</f>
@@ -6356,25 +6356,25 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C23" s="8" t="b">
         <f t="shared" ref="C23:C25" si="2">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C24" s="8" t="b">
         <f t="shared" si="2"/>
@@ -6384,10 +6384,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C25" s="8" t="b">
         <f t="shared" si="2"/>
@@ -6403,10 +6403,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" s="8" t="b">
         <f t="shared" ref="C27:C67" si="3">FALSE()</f>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C28" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C29" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C30" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6455,10 +6455,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C31" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C32" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6481,10 +6481,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C33" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C34" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C35" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C36" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C37" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6546,10 +6546,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C38" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6559,10 +6559,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C39" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6572,10 +6572,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C40" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6585,10 +6585,10 @@
     </row>
     <row r="41" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C41" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="42" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C42" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="43" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C43" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6624,10 +6624,10 @@
     </row>
     <row r="44" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C44" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6637,10 +6637,10 @@
     </row>
     <row r="45" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C45" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6650,10 +6650,10 @@
     </row>
     <row r="46" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C46" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="47" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C47" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="48" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C48" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6687,10 +6687,10 @@
     </row>
     <row r="49" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C49" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="50" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C50" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6711,10 +6711,10 @@
     </row>
     <row r="51" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C51" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6723,10 +6723,10 @@
     </row>
     <row r="52" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C52" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="53" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C53" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6747,10 +6747,10 @@
     </row>
     <row r="54" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C54" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="55" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C55" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="56" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="57" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C57" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6795,10 +6795,10 @@
     </row>
     <row r="58" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C58" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C59" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6819,10 +6819,10 @@
     </row>
     <row r="60" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C60" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="61" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C61" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="62" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C62" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="63" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C63" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="64" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C64" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6879,10 +6879,10 @@
     </row>
     <row r="65" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C65" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="66" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C66" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="67" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C67" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C70" t="b">
         <v>0</v>
@@ -6936,10 +6936,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C71" t="b">
         <v>0</v>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C72" t="b">
         <v>0</v>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C73" t="b">
         <v>1</v>

--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08428C3-A3B6-42C4-BC9A-7A7840D0D4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536C8B00-5D99-4891-B6C8-3CB0D34DD8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="365">
   <si>
     <t>setting_name</t>
   </si>
@@ -1149,6 +1149,9 @@
   </si>
   <si>
     <t>MADtrial - Seguimento Chamada EA</t>
+  </si>
+  <si>
+    <t>SARVAC</t>
   </si>
 </sst>
 </file>
@@ -6056,7 +6059,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -6409,7 +6412,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="8" t="b">
-        <f t="shared" ref="C27:C67" si="3">FALSE()</f>
+        <f t="shared" ref="C27:C68" si="3">FALSE()</f>
         <v>0</v>
       </c>
       <c r="D27" s="8"/>
@@ -6583,25 +6586,24 @@
       </c>
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
-        <v>170</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>364</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="1" t="b">
-        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="C41" t="b">
         <v>0</v>
       </c>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C42" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6611,10 +6613,10 @@
     </row>
     <row r="43" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C43" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6624,10 +6626,10 @@
     </row>
     <row r="44" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C44" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6637,10 +6639,10 @@
     </row>
     <row r="45" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C45" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6650,10 +6652,10 @@
     </row>
     <row r="46" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="C46" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6663,22 +6665,23 @@
     </row>
     <row r="47" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="C47" s="1" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="C48" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6687,10 +6690,10 @@
     </row>
     <row r="49" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="C49" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6699,10 +6702,10 @@
     </row>
     <row r="50" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
       </c>
       <c r="C50" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6711,10 +6714,10 @@
     </row>
     <row r="51" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="C51" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6723,10 +6726,10 @@
     </row>
     <row r="52" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6735,10 +6738,10 @@
     </row>
     <row r="53" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C53" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6747,10 +6750,10 @@
     </row>
     <row r="54" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C54" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6759,10 +6762,10 @@
     </row>
     <row r="55" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C55" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6771,10 +6774,10 @@
     </row>
     <row r="56" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C56" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6783,10 +6786,10 @@
     </row>
     <row r="57" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C57" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6795,10 +6798,10 @@
     </row>
     <row r="58" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="C58" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6807,10 +6810,10 @@
     </row>
     <row r="59" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6818,11 +6821,11 @@
       </c>
     </row>
     <row r="60" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
-        <v>207</v>
+      <c r="A60" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="C60" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6830,11 +6833,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
-        <v>211</v>
+      <c r="A61" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C61" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6843,10 +6846,10 @@
     </row>
     <row r="62" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="C62" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6855,10 +6858,10 @@
     </row>
     <row r="63" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="C63" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6867,7 +6870,7 @@
     </row>
     <row r="64" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>60</v>
@@ -6879,10 +6882,10 @@
     </row>
     <row r="65" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C65" s="1" t="b">
         <f t="shared" si="3"/>
@@ -6890,23 +6893,23 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="A66" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C66" s="8" t="b">
+      <c r="C66" s="1" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>202</v>
+        <v>222</v>
+      </c>
+      <c r="B67" t="s">
+        <v>151</v>
       </c>
       <c r="C67" s="8" t="b">
         <f t="shared" si="3"/>
@@ -6914,29 +6917,30 @@
       </c>
     </row>
     <row r="68" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="A68" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" s="8" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
+    <row r="70" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -6947,7 +6951,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -6958,12 +6962,23 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>134</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>36</v>
       </c>
-      <c r="C73" t="b">
+      <c r="C74" t="b">
         <v>1</v>
       </c>
     </row>

--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536C8B00-5D99-4891-B6C8-3CB0D34DD8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB6E67B-3A40-4DD6-9638-B73F745A7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -1590,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P274"/>
+  <dimension ref="A1:P286"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="1"/>
@@ -4134,13 +4134,24 @@
         <v>128</v>
       </c>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B273" t="s">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D284" t="s">
+        <v>36</v>
+      </c>
+      <c r="F284" t="s">
+        <v>134</v>
+      </c>
+      <c r="I284" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="285" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B274" t="s">
+    <row r="286" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4226,17 +4237,6 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>39</v>

--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB6E67B-3A40-4DD6-9638-B73F745A7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F1A871-AB1C-4704-B84A-99899585D74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>

--- a/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
+++ b/app/config/tables/MADTRIAL_FU_SHORT/Forms/MADTRIAL_FU_SHORT/MADTRIAL_FU_SHORT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MAD_2_2\MADtrial\app\config\tables\MADTRIAL_FU_SHORT\Forms\MADTRIAL_FU_SHORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F1A871-AB1C-4704-B84A-99899585D74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F322BB-2D2B-4EEF-9B93-79F2FE61BF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -1106,42 +1106,12 @@
     <t>DATINC</t>
   </si>
   <si>
-    <t>A criança teve diarréia durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança vomitou  durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança teve tosse  durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança está com constipação  durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança perdeu o seu apetite durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança chorou mais do que o habitual durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança teve febre  durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança teve convulsões (desmaio) durante ultimo semana?</t>
-  </si>
-  <si>
-    <t>A criança teve outras sintomas durante ultimo semana?</t>
-  </si>
-  <si>
     <t>Augusto da Costa</t>
   </si>
   <si>
     <t>Josemira</t>
   </si>
   <si>
-    <t>A criança recebeu medicamentos durante ultimo semana?</t>
-  </si>
-  <si>
     <t>Inclusão/Último seguimento por telefone: &lt;b&gt;{{calculates.displayLASTFUSUC}}&lt;/b&gt;</t>
   </si>
   <si>
@@ -1152,6 +1122,36 @@
   </si>
   <si>
     <t>SARVAC</t>
+  </si>
+  <si>
+    <t>A criança teve convulsões (ataque) durante ultimo semana?</t>
+  </si>
+  <si>
+    <t>A criança chorou mais do que o habitual durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança teve febre  durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança teve outras sintomas durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança perdeu o seu apetite durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança está com constipação  durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança teve tosse  durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança vomitou  durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança teve diarréia durante ultimo semana? (Se sim - este e novo sintoma, ou aquele com que ele(a) saiu do HNSM com?)</t>
+  </si>
+  <si>
+    <t>A criança recebeu medicamentos durante a ultima semana? (Se sim - são novos medicamentos, ou aqueles receitados no HNSM?)</t>
   </si>
 </sst>
 </file>
@@ -1546,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4420,7 +4420,7 @@
         <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.35">
@@ -4437,7 +4437,7 @@
         <v>171</v>
       </c>
       <c r="H25" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
@@ -4461,7 +4461,7 @@
         <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.35">
@@ -4478,7 +4478,7 @@
         <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.35">
@@ -4502,7 +4502,7 @@
         <v>168</v>
       </c>
       <c r="H40" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.35">
@@ -4519,7 +4519,7 @@
         <v>181</v>
       </c>
       <c r="H41" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.35">
@@ -4543,7 +4543,7 @@
         <v>168</v>
       </c>
       <c r="H47" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.35">
@@ -4560,7 +4560,7 @@
         <v>185</v>
       </c>
       <c r="H48" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.35">
@@ -4584,7 +4584,7 @@
         <v>168</v>
       </c>
       <c r="H54" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.35">
@@ -4601,7 +4601,7 @@
         <v>188</v>
       </c>
       <c r="H55" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.35">
@@ -4625,7 +4625,7 @@
         <v>168</v>
       </c>
       <c r="H61" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.35">
@@ -4642,7 +4642,7 @@
         <v>191</v>
       </c>
       <c r="H62" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.35">
@@ -4666,7 +4666,7 @@
         <v>168</v>
       </c>
       <c r="H68" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.35">
@@ -4683,7 +4683,7 @@
         <v>194</v>
       </c>
       <c r="H69" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.35">
@@ -4707,7 +4707,7 @@
         <v>168</v>
       </c>
       <c r="H75" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.35">
@@ -4724,7 +4724,7 @@
         <v>197</v>
       </c>
       <c r="H76" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.35">
@@ -4748,7 +4748,7 @@
         <v>168</v>
       </c>
       <c r="H82" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.35">
@@ -4765,7 +4765,7 @@
         <v>200</v>
       </c>
       <c r="H83" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.35">
@@ -4816,7 +4816,7 @@
         <v>168</v>
       </c>
       <c r="H90" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.35">
@@ -4901,7 +4901,7 @@
         <v>168</v>
       </c>
       <c r="H99" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.35">
@@ -4918,7 +4918,7 @@
         <v>218</v>
       </c>
       <c r="H100" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.35">
@@ -5176,10 +5176,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="G8" s="8"/>
     </row>
@@ -5192,10 +5192,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s">
         <v>60</v>
